--- a/docs-site/public/samples/inventory-gear-product-import-example.xlsx
+++ b/docs-site/public/samples/inventory-gear-product-import-example.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
     <sheet name="Maestros de referencia" sheetId="2" r:id="rId2"/>
+    <sheet name="Productos equivalentes" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="121">
   <si>
     <t>N°</t>
   </si>
@@ -104,61 +105,145 @@
     <t>Descontinuado</t>
   </si>
   <si>
+    <t>860039</t>
+  </si>
+  <si>
+    <t>124192</t>
+  </si>
+  <si>
+    <t>ROTULA/MUÑON SUSP. TOY. COROLLA 92/PSU</t>
+  </si>
+  <si>
+    <t>Suspensión</t>
+  </si>
+  <si>
+    <t>Toyota Genuine</t>
+  </si>
+  <si>
+    <t>Autorepuestos Demo SRL</t>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>WH-001</t>
+  </si>
+  <si>
+    <t>WH-001-B-02-B-01</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>860068</t>
+  </si>
+  <si>
+    <t>124846</t>
+  </si>
+  <si>
+    <t>TERMINAL DE DIRECCION IPSU/CALDINA L</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>WH-001-A-01-B-01</t>
+  </si>
+  <si>
+    <t>860069</t>
+  </si>
+  <si>
+    <t>124847</t>
+  </si>
+  <si>
+    <t>TERMINAL DE DIRECCION IPSU/CALDINA R</t>
+  </si>
+  <si>
+    <t>WH-001-A-02-A-01</t>
+  </si>
+  <si>
+    <t>860153</t>
+  </si>
+  <si>
+    <t>43330-29075</t>
+  </si>
+  <si>
+    <t>MUÑON/ROTULA INF. DE KING LONG 2016-2020</t>
+  </si>
+  <si>
+    <t>TRW</t>
+  </si>
+  <si>
+    <t>WH-001-C-01-A-01</t>
+  </si>
+  <si>
+    <t>860154</t>
+  </si>
+  <si>
+    <t>43350-29095</t>
+  </si>
+  <si>
+    <t>MUÑON/ROTULA SUP KING LONG 2016-2020</t>
+  </si>
+  <si>
+    <t>WH-001-C-01-B-01</t>
+  </si>
+  <si>
+    <t>850027</t>
+  </si>
+  <si>
+    <t>JUNTA COROLLA DIESEL/IPSUCALDINA ABS 26X24 (26X56X24)</t>
+  </si>
+  <si>
+    <t>WH-001-A-02-B-01</t>
+  </si>
+  <si>
+    <t>850000</t>
+  </si>
+  <si>
+    <t>850070</t>
+  </si>
+  <si>
+    <t>CAPUCHON JUNTA C/PRECINTO MET.</t>
+  </si>
+  <si>
+    <t>WH-001-B-02-A-01</t>
+  </si>
+  <si>
     <t>860067</t>
   </si>
   <si>
     <t>MUÑON DIREC. TOY COROLLA/IPSU 84/95</t>
   </si>
   <si>
-    <t>Dirección</t>
-  </si>
-  <si>
-    <t>Toyota Genuine</t>
-  </si>
-  <si>
-    <t>Autorepuestos Demo SRL</t>
-  </si>
-  <si>
-    <t>pcs</t>
-  </si>
-  <si>
-    <t>WH-001</t>
-  </si>
-  <si>
     <t>WH-001-A-01-A-01</t>
   </si>
   <si>
-    <t>860068</t>
-  </si>
-  <si>
-    <t>124846</t>
-  </si>
-  <si>
-    <t>TERMINAL DE DIRECCION IPSU/CALDINA L</t>
-  </si>
-  <si>
-    <t>WH-001-A-01-B-01</t>
-  </si>
-  <si>
-    <t>860069</t>
-  </si>
-  <si>
-    <t>124847</t>
-  </si>
-  <si>
-    <t>TERMINAL DE DIRECCION IPSU/CALDINA R</t>
-  </si>
-  <si>
-    <t>WH-001-A-02-A-01</t>
-  </si>
-  <si>
     <t>860090</t>
   </si>
   <si>
     <t>MUÑON DIR. TOY. HIACE 2002 14X15</t>
   </si>
   <si>
-    <t>WH-001-A-02-B-01</t>
+    <t>860093</t>
+  </si>
+  <si>
+    <t>BRAZO/PRECAP DIR. TOY. COROLLA/CALDINA/HIACE 14X15</t>
+  </si>
+  <si>
+    <t>860144</t>
+  </si>
+  <si>
+    <t>HQ-T26204</t>
+  </si>
+  <si>
+    <t>TERMINAL/MUÑON DIR. KING LONG 99/2004 14X15 MM</t>
+  </si>
+  <si>
+    <t>WH-001-C-02-A-01</t>
   </si>
   <si>
     <t>860030</t>
@@ -170,9 +255,6 @@
     <t>BRAZO DE CREMALLERA HIDRAULICO TOY. 16X14 (16X14X1.5)</t>
   </si>
   <si>
-    <t>TRW</t>
-  </si>
-  <si>
     <t>WH-001-B-01-A-01</t>
   </si>
   <si>
@@ -188,64 +270,49 @@
     <t>WH-001-B-01-B-01</t>
   </si>
   <si>
-    <t>860093</t>
-  </si>
-  <si>
-    <t>BRAZO/PRECAP DIR. TOY. COROLLA/CALDINA/HIACE 14X15</t>
-  </si>
-  <si>
-    <t>WH-001-B-02-A-01</t>
-  </si>
-  <si>
-    <t>860039</t>
-  </si>
-  <si>
-    <t>124192</t>
-  </si>
-  <si>
-    <t>ROTULA/MUÑON SUSP. TOY. COROLLA 92/PSU</t>
-  </si>
-  <si>
-    <t>Suspensión</t>
-  </si>
-  <si>
-    <t>WH-001-B-02-B-01</t>
-  </si>
-  <si>
-    <t>860153</t>
-  </si>
-  <si>
-    <t>43330-29075</t>
-  </si>
-  <si>
-    <t>MUÑON/ROTULA INF. DE KING LONG 2016-2020</t>
-  </si>
-  <si>
-    <t>WH-001-C-01-A-01</t>
-  </si>
-  <si>
-    <t>860154</t>
-  </si>
-  <si>
-    <t>43350-29095</t>
-  </si>
-  <si>
-    <t>MUÑON/ROTULA SUP KING LONG 2016-2020</t>
-  </si>
-  <si>
-    <t>WH-001-C-01-B-01</t>
-  </si>
-  <si>
-    <t>860144</t>
-  </si>
-  <si>
-    <t>HQ-T26204</t>
-  </si>
-  <si>
-    <t>TERMINAL/MUÑON DIR. KING LONG 99/2004 14X15 MM</t>
-  </si>
-  <si>
-    <t>WH-001-C-02-A-01</t>
+    <t>850136</t>
+  </si>
+  <si>
+    <t>RF4950021</t>
+  </si>
+  <si>
+    <t>CAPUCHON TRICETA TOY. NOAH/VOXY 2000 YARIS/CALDINA/RAV4</t>
+  </si>
+  <si>
+    <t>850020</t>
+  </si>
+  <si>
+    <t>TO-1-1010A</t>
+  </si>
+  <si>
+    <t>JUNTA GASOLINA ABS COROLLA 26X23 (26X56X23)</t>
+  </si>
+  <si>
+    <t>120714</t>
+  </si>
+  <si>
+    <t>YOI-192</t>
+  </si>
+  <si>
+    <t>BARRA ESTAB. NOAH DEL 96</t>
+  </si>
+  <si>
+    <t>860026</t>
+  </si>
+  <si>
+    <t>YOI-237</t>
+  </si>
+  <si>
+    <t>BARRA ESTABILIZADORA NOAH TRAS. 99 MUÑON/PERNO</t>
+  </si>
+  <si>
+    <t>860057</t>
+  </si>
+  <si>
+    <t>YOI-240</t>
+  </si>
+  <si>
+    <t>ROTULA/MUÑON SUP. NOAH SIN GRASERA BLINDADO</t>
   </si>
   <si>
     <t>860056</t>
@@ -260,66 +327,6 @@
     <t>WH-001-C-02-B-01</t>
   </si>
   <si>
-    <t>860057</t>
-  </si>
-  <si>
-    <t>YOI-240</t>
-  </si>
-  <si>
-    <t>ROTULA/MUÑON SUP. NOAH SIN GRASERA BLINDADO</t>
-  </si>
-  <si>
-    <t>860026</t>
-  </si>
-  <si>
-    <t>YOI-237</t>
-  </si>
-  <si>
-    <t>BARRA ESTABILIZADORA NOAH TRAS. 99 MUÑON/PERNO</t>
-  </si>
-  <si>
-    <t>120714</t>
-  </si>
-  <si>
-    <t>YOI-192</t>
-  </si>
-  <si>
-    <t>BARRA ESTAB. NOAH DEL 96</t>
-  </si>
-  <si>
-    <t>850027</t>
-  </si>
-  <si>
-    <t>JUNTA COROLLA DIESEL/IPSUCALDINA ABS 26X24 (26X56X24)</t>
-  </si>
-  <si>
-    <t>850020</t>
-  </si>
-  <si>
-    <t>TO-1-1010A</t>
-  </si>
-  <si>
-    <t>JUNTA GASOLINA ABS COROLLA 26X23 (26X56X23)</t>
-  </si>
-  <si>
-    <t>850136</t>
-  </si>
-  <si>
-    <t>RF4950021</t>
-  </si>
-  <si>
-    <t>CAPUCHON TRICETA TOY. NOAH/VOXY 2000 YARIS/CALDINA/RAV4</t>
-  </si>
-  <si>
-    <t>850000</t>
-  </si>
-  <si>
-    <t>850070</t>
-  </si>
-  <si>
-    <t>CAPUCHON JUNTA C/PRECINTO MET.</t>
-  </si>
-  <si>
     <t>Tabla destino</t>
   </si>
   <si>
@@ -338,19 +345,40 @@
     <t>brands</t>
   </si>
   <si>
+    <t>manufacturers</t>
+  </si>
+  <si>
+    <t>Toyota Motor Corp.</t>
+  </si>
+  <si>
+    <t>ZF Group (TRW)</t>
+  </si>
+  <si>
     <t>suppliers</t>
   </si>
   <si>
-    <t>company_name</t>
-  </si>
-  <si>
     <t>warehouses</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
     <t>storage_locations</t>
+  </si>
+  <si>
+    <t>Producto</t>
+  </si>
+  <si>
+    <t>SKU producto</t>
+  </si>
+  <si>
+    <t>Producto equivalente</t>
+  </si>
+  <si>
+    <t>SKU equivalente</t>
+  </si>
+  <si>
+    <t>Nota</t>
+  </si>
+  <si>
+    <t>Ejemplo: productos equivalentes (860067 ↔ 860068).</t>
   </si>
 </sst>
 </file>
@@ -400,11 +428,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -701,8 +730,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AC20"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="6" width="42.7109375" customWidth="1"/>
+    <col min="7" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="11" max="14" width="14.7109375" customWidth="1"/>
+    <col min="15" max="20" width="12.7109375" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" customWidth="1"/>
+    <col min="25" max="26" width="18.7109375" customWidth="1"/>
+    <col min="27" max="28" width="10.7109375" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:29" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -798,35 +842,38 @@
       <c r="B2" t="s">
         <v>29</v>
       </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2">
-        <v>24.5</v>
+        <v>37.1</v>
       </c>
       <c r="L2">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="M2">
-        <v>29.75</v>
+        <v>45.05</v>
       </c>
       <c r="N2">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="O2">
         <v>42.9</v>
@@ -847,19 +894,19 @@
         <v>2</v>
       </c>
       <c r="V2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB2">
-        <v>1</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -867,28 +914,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3">
         <v>53.9</v>
@@ -921,19 +968,19 @@
         <v>2</v>
       </c>
       <c r="V3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB3">
-        <v>1</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -941,28 +988,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
         <v>43</v>
       </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4">
         <v>53.9</v>
@@ -995,19 +1042,19 @@
         <v>2</v>
       </c>
       <c r="V4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB4">
-        <v>1</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1015,37 +1062,40 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K5">
-        <v>47.6</v>
+        <v>77</v>
       </c>
       <c r="L5">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="M5">
-        <v>57.8</v>
+        <v>93.5</v>
       </c>
       <c r="N5">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="O5">
         <v>42.9</v>
@@ -1066,19 +1116,19 @@
         <v>2</v>
       </c>
       <c r="V5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB5">
-        <v>1</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1086,40 +1136,40 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K6">
-        <v>31.5</v>
+        <v>79.8</v>
       </c>
       <c r="L6">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="M6">
-        <v>38.25</v>
+        <v>96.9</v>
       </c>
       <c r="N6">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="O6">
         <v>42.9</v>
@@ -1140,19 +1190,19 @@
         <v>2</v>
       </c>
       <c r="V6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB6">
-        <v>1</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1160,40 +1210,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>31.5</v>
+        <v>120.4</v>
       </c>
       <c r="L7">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="M7">
-        <v>38.25</v>
+        <v>146.2</v>
       </c>
       <c r="N7">
-        <v>52</v>
+        <v>198</v>
       </c>
       <c r="O7">
         <v>42.9</v>
@@ -1214,19 +1261,19 @@
         <v>2</v>
       </c>
       <c r="V7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB7">
-        <v>1</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1234,37 +1281,40 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>61</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8">
+        <v>19.6</v>
+      </c>
+      <c r="L8">
+        <v>28</v>
+      </c>
+      <c r="M8">
+        <v>23.8</v>
+      </c>
+      <c r="N8">
         <v>32</v>
-      </c>
-      <c r="J8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8">
-        <v>40.6</v>
-      </c>
-      <c r="L8">
-        <v>58</v>
-      </c>
-      <c r="M8">
-        <v>49.3</v>
-      </c>
-      <c r="N8">
-        <v>67</v>
       </c>
       <c r="O8">
         <v>42.9</v>
@@ -1285,19 +1335,19 @@
         <v>2</v>
       </c>
       <c r="V8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1305,40 +1355,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K9">
-        <v>37.1</v>
+        <v>24.5</v>
       </c>
       <c r="L9">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="M9">
-        <v>45.05</v>
+        <v>29.75</v>
       </c>
       <c r="N9">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="O9">
         <v>42.9</v>
@@ -1359,19 +1406,19 @@
         <v>2</v>
       </c>
       <c r="V9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB9">
-        <v>1</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1379,40 +1426,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="J10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K10">
-        <v>77</v>
+        <v>47.6</v>
       </c>
       <c r="L10">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="M10">
-        <v>93.5</v>
+        <v>57.8</v>
       </c>
       <c r="N10">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="O10">
         <v>42.9</v>
@@ -1433,19 +1477,19 @@
         <v>2</v>
       </c>
       <c r="V10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB10">
-        <v>1</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1453,9 +1497,6 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
         <v>70</v>
       </c>
       <c r="D11" t="s">
@@ -1468,25 +1509,25 @@
         <v>71</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="J11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K11">
-        <v>79.8</v>
+        <v>40.6</v>
       </c>
       <c r="L11">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="M11">
-        <v>96.9</v>
+        <v>49.3</v>
       </c>
       <c r="N11">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="O11">
         <v>42.9</v>
@@ -1507,19 +1548,19 @@
         <v>2</v>
       </c>
       <c r="V11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB11">
-        <v>1</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1527,28 +1568,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
         <v>73</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" t="s">
         <v>74</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>74</v>
       </c>
-      <c r="E12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" t="s">
-        <v>75</v>
-      </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K12">
         <v>39.9</v>
@@ -1581,19 +1622,19 @@
         <v>2</v>
       </c>
       <c r="V12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z12" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB12">
-        <v>1</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1601,40 +1642,40 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
         <v>77</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" t="s">
         <v>78</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>78</v>
       </c>
-      <c r="E13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" t="s">
-        <v>79</v>
-      </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K13">
-        <v>62.3</v>
+        <v>31.5</v>
       </c>
       <c r="L13">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="M13">
-        <v>75.65</v>
+        <v>38.25</v>
       </c>
       <c r="N13">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="O13">
         <v>42.9</v>
@@ -1655,19 +1696,19 @@
         <v>2</v>
       </c>
       <c r="V13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB13">
-        <v>1</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1675,40 +1716,40 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
         <v>81</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
         <v>82</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>82</v>
       </c>
-      <c r="E14" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" t="s">
-        <v>83</v>
-      </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K14">
-        <v>49.7</v>
+        <v>31.5</v>
       </c>
       <c r="L14">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="M14">
-        <v>60.35</v>
+        <v>38.25</v>
       </c>
       <c r="N14">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="O14">
         <v>42.9</v>
@@ -1729,19 +1770,19 @@
         <v>2</v>
       </c>
       <c r="V14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB14">
-        <v>1</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1764,25 +1805,25 @@
         <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K15">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="L15">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M15">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="N15">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="O15">
         <v>42.9</v>
@@ -1803,19 +1844,19 @@
         <v>2</v>
       </c>
       <c r="V15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z15" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB15">
-        <v>1</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1838,25 +1879,25 @@
         <v>89</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16">
-        <v>32.2</v>
+        <v>113.4</v>
       </c>
       <c r="L16">
-        <v>46</v>
+        <v>162</v>
       </c>
       <c r="M16">
-        <v>39.1</v>
+        <v>137.7</v>
       </c>
       <c r="N16">
-        <v>53</v>
+        <v>186</v>
       </c>
       <c r="O16">
         <v>42.9</v>
@@ -1877,19 +1918,19 @@
         <v>2</v>
       </c>
       <c r="V16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB16">
-        <v>1</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1899,35 +1940,38 @@
       <c r="B17" t="s">
         <v>90</v>
       </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K17">
-        <v>120.4</v>
+        <v>32.2</v>
       </c>
       <c r="L17">
-        <v>172</v>
+        <v>46</v>
       </c>
       <c r="M17">
-        <v>146.2</v>
+        <v>39.1</v>
       </c>
       <c r="N17">
-        <v>198</v>
+        <v>53</v>
       </c>
       <c r="O17">
         <v>42.9</v>
@@ -1948,19 +1992,19 @@
         <v>2</v>
       </c>
       <c r="V17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z17" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB17">
-        <v>1</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -1968,40 +2012,40 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18">
-        <v>113.4</v>
+        <v>42</v>
       </c>
       <c r="L18">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="M18">
-        <v>137.7</v>
+        <v>51</v>
       </c>
       <c r="N18">
-        <v>186</v>
+        <v>69</v>
       </c>
       <c r="O18">
         <v>42.9</v>
@@ -2022,19 +2066,19 @@
         <v>2</v>
       </c>
       <c r="V18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z18" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB18">
-        <v>1</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2042,40 +2086,40 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K19">
-        <v>28</v>
+        <v>49.7</v>
       </c>
       <c r="L19">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="M19">
-        <v>34</v>
+        <v>60.35</v>
       </c>
       <c r="N19">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="O19">
         <v>42.9</v>
@@ -2096,19 +2140,19 @@
         <v>2</v>
       </c>
       <c r="V19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z19" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB19">
-        <v>1</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2116,40 +2160,40 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K20">
-        <v>19.6</v>
+        <v>62.3</v>
       </c>
       <c r="L20">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="M20">
-        <v>23.8</v>
+        <v>75.65</v>
       </c>
       <c r="N20">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="O20">
         <v>42.9</v>
@@ -2170,19 +2214,19 @@
         <v>2</v>
       </c>
       <c r="V20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z20" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB20">
-        <v>1</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
+        <v>102</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2192,73 +2236,78 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="42.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="2" t="s">
         <v>103</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
         <v>107</v>
       </c>
-      <c r="B6" t="s">
-        <v>108</v>
-      </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2266,142 +2315,215 @@
         <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="36.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="42.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="60.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
